--- a/NAUTICA ATS TOM .xlsx
+++ b/NAUTICA ATS TOM .xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafa3\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Estudios y certificaciones\ESTUDIOS DE PROGRAMMING\PROGRAMMING\PERSONAL\PYTHON\Image_Generator_API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7648601B-A4B0-414C-9149-8D2BD628A7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB9DF6C-7C9A-4892-8FD9-1992EFB02E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
